--- a/app/user/styles/file/user_tpl.xlsx
+++ b/app/user/styles/file/user_tpl.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>真实姓名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,6 +67,18 @@
   </si>
   <si>
     <t>冯际成2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部门ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手机号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13389799321</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -128,7 +140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -158,24 +170,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <condense val="0"/>
@@ -498,16 +501,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="12.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="7" customWidth="1"/>
+    <col min="1" max="1" width="12.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="7" customWidth="1"/>
     <col min="4" max="5" width="8.25" style="9" customWidth="1"/>
-    <col min="6" max="6" width="29.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.875" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -526,8 +532,14 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:8">
       <c r="A2" s="4">
         <v>16338</v>
       </c>
@@ -546,8 +558,14 @@
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G2" s="10">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4">
+        <v>15209793953</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -565,15 +583,21 @@
       </c>
       <c r="F3" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="G3" s="10">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:E2">
-    <cfRule type="duplicateValues" dxfId="2" priority="3" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:E3">
-    <cfRule type="duplicateValues" dxfId="1" priority="1" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
